--- a/res/resultados_modelos.xlsx
+++ b/res/resultados_modelos.xlsx
@@ -497,22 +497,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9006558173427253</v>
+        <v>0.9019917415593879</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8552194484333002</v>
+        <v>0.8560548068780146</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7104388968666004</v>
+        <v>0.7121096137560292</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7390804597701149</v>
+        <v>0.7437825332562175</v>
       </c>
       <c r="F3" t="n">
         <v>0.7793939393939394</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7587020648967552</v>
+        <v>0.7611719443622373</v>
       </c>
     </row>
     <row r="4">
@@ -525,10 +525,10 @@
         <v>0.8470974010201603</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8608293751610884</v>
+        <v>0.8608238061047904</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7216587503221767</v>
+        <v>0.7216476122095807</v>
       </c>
       <c r="E4" t="n">
         <v>0.7363966142684402</v>
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9211804712169055</v>
+        <v>0.9228807384017489</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9667154534408483</v>
+        <v>0.967920854965205</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9334309068816966</v>
+        <v>0.9358417099304099</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9259574468085107</v>
+        <v>0.9319148936170213</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6593939393939394</v>
+        <v>0.6636363636363637</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7702654867256636</v>
+        <v>0.7752212389380532</v>
       </c>
     </row>
     <row r="6">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8623998056837503</v>
+        <v>0.8684721884867622</v>
       </c>
       <c r="C8" t="n">
-        <v>0.897704904451563</v>
+        <v>0.9047763172429029</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7954098089031261</v>
+        <v>0.8095526344858057</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6502033701336433</v>
+        <v>0.7388374052232519</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6781818181818182</v>
+        <v>0.5315151515151515</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6638979531296352</v>
+        <v>0.6182587240042299</v>
       </c>
     </row>
     <row r="9">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9203303376244838</v>
+        <v>0.9251882438668934</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9518809142457381</v>
+        <v>0.952747938068412</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9037618284914761</v>
+        <v>0.9054958761368239</v>
       </c>
       <c r="E16" t="n">
-        <v>0.896964856230032</v>
+        <v>0.8983050847457628</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6806060606060607</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7739490006891799</v>
+        <v>0.7910447761194029</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9403692008744231</v>
+        <v>0.9401263055623027</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9769351320004418</v>
+        <v>0.9765409256600022</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9538702640008836</v>
+        <v>0.9530818513200043</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9347336834208552</v>
+        <v>0.9320388349514563</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7551515151515151</v>
+        <v>0.7563636363636363</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8354006034193764</v>
+        <v>0.835061893609903</v>
       </c>
     </row>
   </sheetData>
